--- a/data/chart/input/old_chart_31/工作簿.xlsx
+++ b/data/chart/input/old_chart_31/工作簿.xlsx
@@ -5,24 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zengyantao/Documents/办公标注/交付/1.2/input/DLG_290/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zengyantao/Documents/办公标注/交付/1.2/可视化/input/old_chart_31/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE3FB01-95A7-1B4D-9FB7-81CD472FB622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29C1BC6-18BB-3D46-96DC-C90E2F374A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="2024" sheetId="2" r:id="rId2"/>
-    <sheet name="2023" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="164">
   <si>
     <t>总数</t>
   </si>
@@ -508,598 +506,6 @@
   </si>
   <si>
     <t>0.000641146520166045</t>
-  </si>
-  <si>
-    <t>案号</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>单位或个人</t>
-  </si>
-  <si>
-    <t>国有、非国有</t>
-  </si>
-  <si>
-    <t>涉案人数</t>
-  </si>
-  <si>
-    <t>犯罪形式</t>
-  </si>
-  <si>
-    <t>罪名</t>
-  </si>
-  <si>
-    <t>裁判结果</t>
-  </si>
-  <si>
-    <t>链接</t>
-  </si>
-  <si>
-    <t>涉案金额</t>
-  </si>
-  <si>
-    <t>（2024）宁0202刑初142号</t>
-  </si>
-  <si>
-    <t>和泰传媒有限公司</t>
-  </si>
-  <si>
-    <t>个人（国）</t>
-  </si>
-  <si>
-    <t>国有</t>
-  </si>
-  <si>
-    <t>经济利益确认中标</t>
-  </si>
-  <si>
-    <t>田丽娟</t>
-  </si>
-  <si>
-    <t>14.9w</t>
-  </si>
-  <si>
-    <t>（2024）浙0702刑初615号</t>
-  </si>
-  <si>
-    <t>个人（非国）</t>
-  </si>
-  <si>
-    <t>非国有</t>
-  </si>
-  <si>
-    <t>伙同投标人相互串通投标报价</t>
-  </si>
-  <si>
-    <t>兰金电子网络有限公司</t>
-  </si>
-  <si>
-    <t>78.85w</t>
-  </si>
-  <si>
-    <t>（2024）新4002刑初176号</t>
-  </si>
-  <si>
-    <t>杨坤</t>
-  </si>
-  <si>
-    <t>李桂花</t>
-  </si>
-  <si>
-    <t>覃凤兰</t>
-  </si>
-  <si>
-    <t>56.192284万元</t>
-  </si>
-  <si>
-    <t>（2024）新2328刑初9号</t>
-  </si>
-  <si>
-    <t>许某受贿罪刑事一审刑事判决书</t>
-  </si>
-  <si>
-    <t>娄成</t>
-  </si>
-  <si>
-    <t>凌强</t>
-  </si>
-  <si>
-    <t>295．524622万元</t>
-  </si>
-  <si>
-    <t>（2024）鄂0984刑初349号</t>
-  </si>
-  <si>
-    <t>邵桂香</t>
-  </si>
-  <si>
-    <t>张淑华</t>
-  </si>
-  <si>
-    <t>判处拘役五个月，缓刑七个月，并处罚金人民币6000元</t>
-  </si>
-  <si>
-    <t>10100</t>
-  </si>
-  <si>
-    <t>（2024）川1322刑初11号</t>
-  </si>
-  <si>
-    <t>邱玉</t>
-  </si>
-  <si>
-    <t>决定将原定的15个标段合并成两个大标段进行招标，通过设定特定条件操控招投标，由特定公司参与投标，再划分多个施工段，交给特定人员承建。</t>
-  </si>
-  <si>
-    <t>判处有期徒刑七年六个月，并处罚金人民币30万元</t>
-  </si>
-  <si>
-    <t>3253915元</t>
-  </si>
-  <si>
-    <t>（2024）青2801刑初83号</t>
-  </si>
-  <si>
-    <t>戚某贪污罪刑事一审刑事判决书</t>
-  </si>
-  <si>
-    <t>对方是国家工作人员</t>
-  </si>
-  <si>
-    <t>思优网络有限公司</t>
-  </si>
-  <si>
-    <t>精芯传媒有限公司</t>
-  </si>
-  <si>
-    <t>行贿罪，判处有期徒刑六个月，并处罚金人民币10万元；犯贪污罪，判处有期徒刑一年，并处罚金人民币20万元。数罪并罚，决定执行有期徒刑一年二个月，并处罚金人民币30万元</t>
-  </si>
-  <si>
-    <t>（2024）青0103刑初230号</t>
-  </si>
-  <si>
-    <t>党某串通投标罪刑事一审刑事判决书</t>
-  </si>
-  <si>
-    <t>非</t>
-  </si>
-  <si>
-    <t>朱丽华</t>
-  </si>
-  <si>
-    <t>判处有期徒刑七个月，并处罚金人民币二万元，与原判刑罚有期徒刑五年三个月，并处罚金人民币二十万元，数罪并罚，决定执行有期徒刑五年六个月，并处罚金人民币二十二万元。</t>
-  </si>
-  <si>
-    <t>28495154</t>
-  </si>
-  <si>
-    <t>（2024）新2222刑初31号</t>
-  </si>
-  <si>
-    <t>包某串通投标罪受贿罪刑事一审刑事判决书</t>
-  </si>
-  <si>
-    <t>张芳</t>
-  </si>
-  <si>
-    <t>被告人包某犯串通投标罪，判处罚金人民币1.5万元；犯受贿罪，判处有期徒刑二年，并处罚金人民币20万元；决定执行有期徒刑二年，并处罚金人民币21.5万元（罚金已缴纳）；</t>
-  </si>
-  <si>
-    <t>21w</t>
-  </si>
-  <si>
-    <t>（2024）新2222刑初32号</t>
-  </si>
-  <si>
-    <t>李敏</t>
-  </si>
-  <si>
-    <t>张鹏</t>
-  </si>
-  <si>
-    <t>许秀华</t>
-  </si>
-  <si>
-    <t>（2024）川1528刑初36号</t>
-  </si>
-  <si>
-    <t>李鹏</t>
-  </si>
-  <si>
-    <t>郑秀云</t>
-  </si>
-  <si>
-    <t>被告人孙某成犯受贿罪，判处有期徒刑二年，缓刑三年，</t>
-  </si>
-  <si>
-    <t>53w</t>
-  </si>
-  <si>
-    <t>（2023）沪0105刑初332号</t>
-  </si>
-  <si>
-    <t>吴洁</t>
-  </si>
-  <si>
-    <t>共谋，指使被告人杨某2以某某公司2名义参与某某公司1招投标，并在某某公司2报价基础上增加部分金额向某某公司1报价。</t>
-  </si>
-  <si>
-    <t>高瑞</t>
-  </si>
-  <si>
-    <t>（2024）浙0402刑初225号</t>
-  </si>
-  <si>
-    <t>图龙信息传媒有限公司</t>
-  </si>
-  <si>
-    <t xml:space="preserve">被告人甲犯串通投标罪，判处有期徒刑七个月，缓刑一年，并处罚金十万元。被告人乙犯串通投标罪，判处拘役五个月，缓刑九个月，并处罚金五万元。被告人丙犯串通投标罪，判处拘役四个月，缓刑七个月，并处罚金四万元。 </t>
-  </si>
-  <si>
-    <t>428316.5</t>
-  </si>
-  <si>
-    <t>（2024）青2891刑初3号</t>
-  </si>
-  <si>
-    <t>唐某贪污罪刑事一审刑事判决书</t>
-  </si>
-  <si>
-    <t>王冬梅</t>
-  </si>
-  <si>
-    <t>四通传媒有限公司</t>
-  </si>
-  <si>
-    <t>870.039w</t>
-  </si>
-  <si>
-    <t>（2024）赣0922刑初127号</t>
-  </si>
-  <si>
-    <t>韦淑兰</t>
-  </si>
-  <si>
-    <t>017年万载县某项目网上公开招投标，该项目共20个标段，总投资金额约10894万元，招标方式为合理低价法。</t>
-  </si>
-  <si>
-    <t>逯桂芝</t>
-  </si>
-  <si>
-    <t>145w</t>
-  </si>
-  <si>
-    <t>（2024）青2891刑初4号</t>
-  </si>
-  <si>
-    <t>杨瑜</t>
-  </si>
-  <si>
-    <t>李桂荣</t>
-  </si>
-  <si>
-    <t>晏秀珍</t>
-  </si>
-  <si>
-    <t>(2024)渝0116刑初4号</t>
-  </si>
-  <si>
-    <t>秦某受贿罪一审刑事判决书</t>
-  </si>
-  <si>
-    <t>被告人秦某犯受贿罪，判处有期徒刑二年六个月，并处罚金人民币二十万元。</t>
-  </si>
-  <si>
-    <t>75.1万元</t>
-  </si>
-  <si>
-    <t>（2023）青0103刑初305号</t>
-  </si>
-  <si>
-    <t>班柳</t>
-  </si>
-  <si>
-    <t>张凤兰</t>
-  </si>
-  <si>
-    <t>（2024）豫0781刑初64号</t>
-  </si>
-  <si>
-    <t>邱某串通投标一审刑事判决书</t>
-  </si>
-  <si>
-    <t>梁玉</t>
-  </si>
-  <si>
-    <t>方勇</t>
-  </si>
-  <si>
-    <t>（2024）青2223刑初1号</t>
-  </si>
-  <si>
-    <t>济南亿次元信息有限公司</t>
-  </si>
-  <si>
-    <t>杨明</t>
-  </si>
-  <si>
-    <t>（2024）浙0402刑初102号</t>
-  </si>
-  <si>
-    <t>102受贿罪一审刑事判决书</t>
-  </si>
-  <si>
-    <t>华泰通安传媒有限公司</t>
-  </si>
-  <si>
-    <t>被告人甲犯受贿罪，判处有期徒刑三年二个月，并处罚金二十万元。</t>
-  </si>
-  <si>
-    <t>827320</t>
-  </si>
-  <si>
-    <t>（2024）浙0482刑初140号</t>
-  </si>
-  <si>
-    <t>2024浙0482刑初140号刑事判决书</t>
-  </si>
-  <si>
-    <t>四通信息有限公司</t>
-  </si>
-  <si>
-    <t>被告人甲犯串通投标罪，判处有期徒刑六个月，缓刑一年，并处罚金八万元</t>
-  </si>
-  <si>
-    <t>（2023）吉0182刑初634号</t>
-  </si>
-  <si>
-    <t>罗秀荣</t>
-  </si>
-  <si>
-    <t>2012年某村建设水泥路工程没有采取招投标的方式。</t>
-  </si>
-  <si>
-    <t>徐玉珍</t>
-  </si>
-  <si>
-    <t>三十五万元</t>
-  </si>
-  <si>
-    <t>（2024）豫0225刑初70号</t>
-  </si>
-  <si>
-    <t>杨敏</t>
-  </si>
-  <si>
-    <t>姜健</t>
-  </si>
-  <si>
-    <t>黄林</t>
-  </si>
-  <si>
-    <t>4495820.22</t>
-  </si>
-  <si>
-    <t>（2023）新3222刑初368号</t>
-  </si>
-  <si>
-    <t>曾颖</t>
-  </si>
-  <si>
-    <t>九方信息有限公司</t>
-  </si>
-  <si>
-    <t>张志强</t>
-  </si>
-  <si>
-    <t>2,273.8456312万</t>
-  </si>
-  <si>
-    <t>（2024）皖1125刑初55号</t>
-  </si>
-  <si>
-    <t>徐某戴某等刑事一审刑事判决书</t>
-  </si>
-  <si>
-    <t>明腾网络有限公司</t>
-  </si>
-  <si>
-    <t>华成育卓信息有限公司</t>
-  </si>
-  <si>
-    <t>舒浩</t>
-  </si>
-  <si>
-    <t>11643655.22</t>
-  </si>
-  <si>
-    <t>（2024）青0105刑初97号</t>
-  </si>
-  <si>
-    <t>罗敏</t>
-  </si>
-  <si>
-    <t>赵玉梅</t>
-  </si>
-  <si>
-    <t>简欣</t>
-  </si>
-  <si>
-    <t>60w</t>
-  </si>
-  <si>
-    <t>（2023）鲁0902刑初428号</t>
-  </si>
-  <si>
-    <t>滕某某马某等串通投标罪串通投标罪刑事一审刑事判决书</t>
-  </si>
-  <si>
-    <t>黄利</t>
-  </si>
-  <si>
-    <t>王霞</t>
-  </si>
-  <si>
-    <t>1796.925</t>
-  </si>
-  <si>
-    <t>（2023）青0223刑初275号</t>
-  </si>
-  <si>
-    <t>郭静</t>
-  </si>
-  <si>
-    <t>傅秀华</t>
-  </si>
-  <si>
-    <t>万迅电脑信息有限公司</t>
-  </si>
-  <si>
-    <t>房红</t>
-  </si>
-  <si>
-    <t>46.2w</t>
-  </si>
-  <si>
-    <t>（2024）浙0303刑初30号</t>
-  </si>
-  <si>
-    <t>正坚建设有限公司易会丰串通投标罪一审刑事判决书</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>联通时科信息有限公司</t>
-  </si>
-  <si>
-    <t>一、被告单位正坚建设有限公司犯串通投标罪，判处罚金人民币300000元（已缴纳）。 
-二、被告人易会丰犯串通投标罪，判处有期徒刑一年六个月，缓刑一年八个月，并处罚金人民币80000元（已缴纳）。 
-（缓刑考验期限，从判决确定之日起计算。在缓刑考验期限内，应接受社区矫正，服从社区矫正机构的监督管理。） 
-三、被告单位正坚建设有限公司退出的违法所得人民币5008078元予以没收，上缴国库。</t>
-  </si>
-  <si>
-    <t>129826888</t>
-  </si>
-  <si>
-    <t>（2023）浙0203刑初1134号</t>
-  </si>
-  <si>
-    <t>应浩曹瞻串通投标罪一审刑事判决书</t>
-  </si>
-  <si>
-    <t xml:space="preserve">被告人应浩、曹瞻、周某、潘某、田某等人建立微信群组成投标团队，在微信群内由被告人应浩发布政府公示的招标项目，为增加中标概率，被告人应浩、曹瞻及周某、潘某、田某等人利用控制、收集的公司通过统一分布控制报价等手段进行串通投标，许诺中标后中标公司可拿2-3个点的好处费，陪标公司也可获取部分好处费。 </t>
-  </si>
-  <si>
-    <t>艾桂英</t>
-  </si>
-  <si>
-    <t>创联世纪网络有限公司</t>
-  </si>
-  <si>
-    <t>（2024）浙0723刑初24号</t>
-  </si>
-  <si>
-    <t>黄建军</t>
-  </si>
-  <si>
-    <t>朱霞</t>
-  </si>
-  <si>
-    <t>宋静</t>
-  </si>
-  <si>
-    <t>（2024）浙0726刑初22号</t>
-  </si>
-  <si>
-    <t>柳兰英</t>
-  </si>
-  <si>
-    <t>晖来计算机网络有限公司</t>
-  </si>
-  <si>
-    <t>甘欢</t>
-  </si>
-  <si>
-    <t>（2024）粤0115刑初22号</t>
-  </si>
-  <si>
-    <t>黄俊</t>
-  </si>
-  <si>
-    <t>汪英</t>
-  </si>
-  <si>
-    <t>黄金凤</t>
-  </si>
-  <si>
-    <t>（2023）粤2072刑初1225号</t>
-  </si>
-  <si>
-    <t>李刚</t>
-  </si>
-  <si>
-    <t>张玉梅</t>
-  </si>
-  <si>
-    <t>（2024）桂1322刑初22号</t>
-  </si>
-  <si>
-    <t>宋畅</t>
-  </si>
-  <si>
-    <t>杨宁</t>
-  </si>
-  <si>
-    <t>黄丽</t>
-  </si>
-  <si>
-    <t>201757880</t>
-  </si>
-  <si>
-    <t>（2024）浙0881刑初18号</t>
-  </si>
-  <si>
-    <t>林庆华串通投标罪一审刑事判决书</t>
-  </si>
-  <si>
-    <t>明腾信息有限公司</t>
-  </si>
-  <si>
-    <t>史梅</t>
-  </si>
-  <si>
-    <t>（2024）浙0703刑初14号</t>
-  </si>
-  <si>
-    <t>曾利</t>
-  </si>
-  <si>
-    <t>邹彬</t>
-  </si>
-  <si>
-    <t>一、被告人邢朝阳犯受贿罪，判处有期徒刑三年六个月，并处罚金人民币二十八万元。（刑期从判决执行之日起计算。判决执行以前先行羁押、留置的，羁押、留置一日折抵刑期一日。即自2023年9月8日起至2027年3月7日止。罚金限判决生效后十日内缴纳）。 
-二、被告人邢朝阳退缴的违法所得人民币一百一十三万四千八百八十四元，依法予以没收，上缴国库。</t>
-  </si>
-  <si>
-    <t>（2023）浙0483刑初913号</t>
-  </si>
-  <si>
-    <t>良诺科技有限公司</t>
-  </si>
-  <si>
-    <t xml:space="preserve">利用技术手段非法侵入浙江省综合性评标专家库获取具体招投标项目的评标专家姓名、联系方式、工作单位等个人信息，后被告人X受Z1委托联系评标专家并以行贿方式让评标专家打高分。项目中标后，被告人X按照事先约定送给评标专家T（已不起诉）由L出资的行贿款14万元。 </t>
-  </si>
-  <si>
-    <t>银嘉网络有限公司</t>
-  </si>
-  <si>
-    <t>艾提科信网络有限公司</t>
-  </si>
-  <si>
-    <t>125w</t>
   </si>
   <si>
     <t>公司A</t>
@@ -1697,7 +1103,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>358</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -1797,7 +1203,7 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>163</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
@@ -2250,1073 +1656,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>188</v>
-      </c>
-      <c r="J4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" t="s">
-        <v>192</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>193</v>
-      </c>
-      <c r="J5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>195</v>
-      </c>
-      <c r="B6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" t="s">
-        <v>198</v>
-      </c>
-      <c r="J6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D7" t="s">
-        <v>175</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>203</v>
-      </c>
-      <c r="J7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" t="s">
-        <v>207</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G8" t="s">
-        <v>209</v>
-      </c>
-      <c r="H8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" t="s">
-        <v>214</v>
-      </c>
-      <c r="G9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J9" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" t="s">
-        <v>218</v>
-      </c>
-      <c r="D10" t="s">
-        <v>181</v>
-      </c>
-      <c r="E10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" t="s">
-        <v>219</v>
-      </c>
-      <c r="G10" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" t="s">
-        <v>220</v>
-      </c>
-      <c r="J10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" t="s">
-        <v>223</v>
-      </c>
-      <c r="C11" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E11" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" t="s">
-        <v>224</v>
-      </c>
-      <c r="G11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>226</v>
-      </c>
-      <c r="B12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C12" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" t="s">
-        <v>175</v>
-      </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s">
-        <v>228</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" t="s">
-        <v>229</v>
-      </c>
-      <c r="J12" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>231</v>
-      </c>
-      <c r="B13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D13" t="s">
-        <v>181</v>
-      </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" t="s">
-        <v>233</v>
-      </c>
-      <c r="G13" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>235</v>
-      </c>
-      <c r="C14" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14" t="s">
-        <v>236</v>
-      </c>
-      <c r="G14" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" t="s">
-        <v>237</v>
-      </c>
-      <c r="J14" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>239</v>
-      </c>
-      <c r="B15" t="s">
-        <v>240</v>
-      </c>
-      <c r="C15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D15" t="s">
-        <v>181</v>
-      </c>
-      <c r="E15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" t="s">
-        <v>241</v>
-      </c>
-      <c r="G15" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" t="s">
-        <v>242</v>
-      </c>
-      <c r="J15" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>244</v>
-      </c>
-      <c r="B16" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" t="s">
-        <v>180</v>
-      </c>
-      <c r="D16" t="s">
-        <v>181</v>
-      </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" t="s">
-        <v>246</v>
-      </c>
-      <c r="G16" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16" t="s">
-        <v>247</v>
-      </c>
-      <c r="J16" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>249</v>
-      </c>
-      <c r="B17" t="s">
-        <v>250</v>
-      </c>
-      <c r="C17" t="s">
-        <v>174</v>
-      </c>
-      <c r="D17" t="s">
-        <v>181</v>
-      </c>
-      <c r="E17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" t="s">
-        <v>251</v>
-      </c>
-      <c r="G17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>253</v>
-      </c>
-      <c r="B18" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" t="s">
-        <v>174</v>
-      </c>
-      <c r="D18" t="s">
-        <v>181</v>
-      </c>
-      <c r="E18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" t="s">
-        <v>255</v>
-      </c>
-      <c r="J18" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>257</v>
-      </c>
-      <c r="C19" t="s">
-        <v>174</v>
-      </c>
-      <c r="D19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" t="s">
-        <v>258</v>
-      </c>
-      <c r="G19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>260</v>
-      </c>
-      <c r="B20" t="s">
-        <v>261</v>
-      </c>
-      <c r="C20" t="s">
-        <v>180</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>262</v>
-      </c>
-      <c r="G20" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>264</v>
-      </c>
-      <c r="C21" t="s">
-        <v>180</v>
-      </c>
-      <c r="D21" t="s">
-        <v>181</v>
-      </c>
-      <c r="E21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" t="s">
-        <v>265</v>
-      </c>
-      <c r="G21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H21" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>267</v>
-      </c>
-      <c r="B22" t="s">
-        <v>268</v>
-      </c>
-      <c r="C22" t="s">
-        <v>174</v>
-      </c>
-      <c r="D22" t="s">
-        <v>175</v>
-      </c>
-      <c r="E22" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" t="s">
-        <v>269</v>
-      </c>
-      <c r="G22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" t="s">
-        <v>270</v>
-      </c>
-      <c r="J22" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>272</v>
-      </c>
-      <c r="B23" t="s">
-        <v>273</v>
-      </c>
-      <c r="C23" t="s">
-        <v>180</v>
-      </c>
-      <c r="E23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" t="s">
-        <v>274</v>
-      </c>
-      <c r="G23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H23" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>276</v>
-      </c>
-      <c r="B24" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" t="s">
-        <v>180</v>
-      </c>
-      <c r="D24" t="s">
-        <v>175</v>
-      </c>
-      <c r="F24" t="s">
-        <v>278</v>
-      </c>
-      <c r="G24" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" t="s">
-        <v>279</v>
-      </c>
-      <c r="J24" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>281</v>
-      </c>
-      <c r="B25" t="s">
-        <v>282</v>
-      </c>
-      <c r="C25" t="s">
-        <v>180</v>
-      </c>
-      <c r="D25" t="s">
-        <v>175</v>
-      </c>
-      <c r="F25" t="s">
-        <v>283</v>
-      </c>
-      <c r="G25" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25" t="s">
-        <v>284</v>
-      </c>
-      <c r="J25" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" t="s">
-        <v>286</v>
-      </c>
-      <c r="B26" t="s">
-        <v>287</v>
-      </c>
-      <c r="C26" t="s">
-        <v>180</v>
-      </c>
-      <c r="F26" t="s">
-        <v>288</v>
-      </c>
-      <c r="G26" t="s">
-        <v>86</v>
-      </c>
-      <c r="H26" t="s">
-        <v>289</v>
-      </c>
-      <c r="J26" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" t="s">
-        <v>291</v>
-      </c>
-      <c r="B27" t="s">
-        <v>292</v>
-      </c>
-      <c r="C27" t="s">
-        <v>180</v>
-      </c>
-      <c r="E27" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" t="s">
-        <v>293</v>
-      </c>
-      <c r="G27" t="s">
-        <v>294</v>
-      </c>
-      <c r="H27" t="s">
-        <v>295</v>
-      </c>
-      <c r="J27" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" t="s">
-        <v>297</v>
-      </c>
-      <c r="B28" t="s">
-        <v>298</v>
-      </c>
-      <c r="C28" t="s">
-        <v>180</v>
-      </c>
-      <c r="E28" t="s">
-        <v>46</v>
-      </c>
-      <c r="F28" t="s">
-        <v>299</v>
-      </c>
-      <c r="G28" t="s">
-        <v>293</v>
-      </c>
-      <c r="H28" t="s">
-        <v>300</v>
-      </c>
-      <c r="J28" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" t="s">
-        <v>302</v>
-      </c>
-      <c r="B29" t="s">
-        <v>303</v>
-      </c>
-      <c r="C29" t="s">
-        <v>180</v>
-      </c>
-      <c r="E29" t="s">
-        <v>85</v>
-      </c>
-      <c r="F29" t="s">
-        <v>304</v>
-      </c>
-      <c r="G29" t="s">
-        <v>86</v>
-      </c>
-      <c r="H29" t="s">
-        <v>305</v>
-      </c>
-      <c r="J29" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" t="s">
-        <v>307</v>
-      </c>
-      <c r="B31" t="s">
-        <v>308</v>
-      </c>
-      <c r="C31" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" t="s">
-        <v>309</v>
-      </c>
-      <c r="G31" t="s">
-        <v>310</v>
-      </c>
-      <c r="H31" t="s">
-        <v>311</v>
-      </c>
-      <c r="J31" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" t="s">
-        <v>313</v>
-      </c>
-      <c r="B32" t="s">
-        <v>314</v>
-      </c>
-      <c r="C32" t="s">
-        <v>315</v>
-      </c>
-      <c r="D32" t="s">
-        <v>181</v>
-      </c>
-      <c r="F32" t="s">
-        <v>316</v>
-      </c>
-      <c r="G32" t="s">
-        <v>86</v>
-      </c>
-      <c r="H32" t="s">
-        <v>317</v>
-      </c>
-      <c r="J32" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>319</v>
-      </c>
-      <c r="B33" t="s">
-        <v>320</v>
-      </c>
-      <c r="C33" t="s">
-        <v>180</v>
-      </c>
-      <c r="E33" t="s">
-        <v>85</v>
-      </c>
-      <c r="F33" t="s">
-        <v>321</v>
-      </c>
-      <c r="G33" t="s">
-        <v>86</v>
-      </c>
-      <c r="H33" t="s">
-        <v>322</v>
-      </c>
-      <c r="J33" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" t="s">
-        <v>324</v>
-      </c>
-      <c r="B34" t="s">
-        <v>325</v>
-      </c>
-      <c r="C34" t="s">
-        <v>180</v>
-      </c>
-      <c r="E34" t="s">
-        <v>54</v>
-      </c>
-      <c r="F34" t="s">
-        <v>326</v>
-      </c>
-      <c r="G34" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" t="s">
-        <v>328</v>
-      </c>
-      <c r="B35" t="s">
-        <v>329</v>
-      </c>
-      <c r="C35" t="s">
-        <v>180</v>
-      </c>
-      <c r="E35" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" t="s">
-        <v>330</v>
-      </c>
-      <c r="G35" t="s">
-        <v>86</v>
-      </c>
-      <c r="H35" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" t="s">
-        <v>332</v>
-      </c>
-      <c r="B36" t="s">
-        <v>333</v>
-      </c>
-      <c r="C36" t="s">
-        <v>315</v>
-      </c>
-      <c r="D36" t="s">
-        <v>181</v>
-      </c>
-      <c r="E36" t="s">
-        <v>46</v>
-      </c>
-      <c r="F36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G36" t="s">
-        <v>71</v>
-      </c>
-      <c r="H36" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>336</v>
-      </c>
-      <c r="B37" t="s">
-        <v>219</v>
-      </c>
-      <c r="C37" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F37" t="s">
-        <v>337</v>
-      </c>
-      <c r="G37" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" t="s">
-        <v>339</v>
-      </c>
-      <c r="B38" t="s">
-        <v>340</v>
-      </c>
-      <c r="C38" t="s">
-        <v>180</v>
-      </c>
-      <c r="E38" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" t="s">
-        <v>341</v>
-      </c>
-      <c r="G38" t="s">
-        <v>86</v>
-      </c>
-      <c r="H38" t="s">
-        <v>342</v>
-      </c>
-      <c r="J38" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>344</v>
-      </c>
-      <c r="B39" t="s">
-        <v>345</v>
-      </c>
-      <c r="C39" t="s">
-        <v>180</v>
-      </c>
-      <c r="E39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F39" t="s">
-        <v>346</v>
-      </c>
-      <c r="G39" t="s">
-        <v>86</v>
-      </c>
-      <c r="H39" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" t="s">
-        <v>348</v>
-      </c>
-      <c r="B40" t="s">
-        <v>349</v>
-      </c>
-      <c r="C40" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40" t="s">
-        <v>46</v>
-      </c>
-      <c r="F40" t="s">
-        <v>350</v>
-      </c>
-      <c r="G40" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" t="s">
-        <v>352</v>
-      </c>
-      <c r="B41" t="s">
-        <v>353</v>
-      </c>
-      <c r="C41" t="s">
-        <v>180</v>
-      </c>
-      <c r="E41" t="s">
-        <v>46</v>
-      </c>
-      <c r="F41" t="s">
-        <v>354</v>
-      </c>
-      <c r="G41" t="s">
-        <v>355</v>
-      </c>
-      <c r="H41" t="s">
-        <v>356</v>
-      </c>
-      <c r="J41" t="s">
-        <v>357</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3486,13 +1825,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2C09B0A-1B42-42A1-B396-DD107FDCA4BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE7CBAA-10E2-4970-9EE2-029A6F3A4301}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3639620E-6FB6-45FE-9570-26BC644DBC78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAEF465B-EB09-4407-A168-4CE98E5A666C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{033D4345-2FA5-45B3-B28C-DC545535DC4D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43426F37-0E96-4F8A-A63C-8DA4AFF3D412}"/>
 </file>